--- a/evaluations/test_reports/throughput/Elapsed_Time/10_Client/direct_client/extracted_stats.xlsx
+++ b/evaluations/test_reports/throughput/Elapsed_Time/10_Client/direct_client/extracted_stats.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D49"/>
+  <dimension ref="A1:D39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -452,105 +452,105 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>1681823294</v>
+        <v>1681823304</v>
       </c>
       <c r="B2" t="n">
         <v>10</v>
       </c>
       <c r="C2" t="n">
-        <v>141.625</v>
+        <v>151</v>
       </c>
       <c r="D2" t="n">
-        <v>41.38711372132261</v>
+        <v>40.90210085276541</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>1681823295</v>
+        <v>1681823305</v>
       </c>
       <c r="B3" t="n">
         <v>10</v>
       </c>
       <c r="C3" t="n">
-        <v>138.3</v>
+        <v>153.3</v>
       </c>
       <c r="D3" t="n">
-        <v>41.34472960856424</v>
+        <v>40.8794330447282</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>1681823296</v>
+        <v>1681823306</v>
       </c>
       <c r="B4" t="n">
         <v>10</v>
       </c>
       <c r="C4" t="n">
-        <v>148.2</v>
+        <v>152.3</v>
       </c>
       <c r="D4" t="n">
-        <v>41.21400587958708</v>
+        <v>40.93572596767061</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>1681823297</v>
+        <v>1681823307</v>
       </c>
       <c r="B5" t="n">
         <v>10</v>
       </c>
       <c r="C5" t="n">
-        <v>148.2</v>
+        <v>155.1</v>
       </c>
       <c r="D5" t="n">
-        <v>40.73990487981234</v>
+        <v>40.79148807370999</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>1681823298</v>
+        <v>1681823308</v>
       </c>
       <c r="B6" t="n">
         <v>10</v>
       </c>
       <c r="C6" t="n">
-        <v>146.1</v>
+        <v>152.2</v>
       </c>
       <c r="D6" t="n">
-        <v>40.14022715944128</v>
+        <v>40.77250345618324</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1681823299</v>
+        <v>1681823309</v>
       </c>
       <c r="B7" t="n">
         <v>10</v>
       </c>
       <c r="C7" t="n">
-        <v>149.2</v>
+        <v>150.5</v>
       </c>
       <c r="D7" t="n">
-        <v>40.69768229167755</v>
+        <v>40.64237352285405</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>1681823300</v>
+        <v>1681823310</v>
       </c>
       <c r="B8" t="n">
         <v>10</v>
       </c>
       <c r="C8" t="n">
-        <v>151.7</v>
+        <v>146.6</v>
       </c>
       <c r="D8" t="n">
-        <v>40.56371530977453</v>
+        <v>40.78167782628478</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>1681823301</v>
+        <v>1681823311</v>
       </c>
       <c r="B9" t="n">
         <v>10</v>
@@ -559,566 +559,426 @@
         <v>151.1</v>
       </c>
       <c r="D9" t="n">
-        <v>40.80681507348289</v>
+        <v>40.63880730350063</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>1681823302</v>
+        <v>1681823312</v>
       </c>
       <c r="B10" t="n">
         <v>10</v>
       </c>
       <c r="C10" t="n">
-        <v>151.6</v>
+        <v>150.6</v>
       </c>
       <c r="D10" t="n">
-        <v>40.84358639035418</v>
+        <v>40.59672463925506</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>1681823303</v>
+        <v>1681823313</v>
       </c>
       <c r="B11" t="n">
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>148.9</v>
+        <v>152.5</v>
       </c>
       <c r="D11" t="n">
-        <v>40.98363942727573</v>
+        <v>40.45908164104623</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>1681823304</v>
+        <v>1681823314</v>
       </c>
       <c r="B12" t="n">
         <v>10</v>
       </c>
       <c r="C12" t="n">
-        <v>151</v>
+        <v>153.3</v>
       </c>
       <c r="D12" t="n">
-        <v>40.90210085276541</v>
+        <v>40.5832706935822</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>1681823305</v>
+        <v>1681823315</v>
       </c>
       <c r="B13" t="n">
         <v>10</v>
       </c>
       <c r="C13" t="n">
-        <v>153.3</v>
+        <v>156.2</v>
       </c>
       <c r="D13" t="n">
-        <v>40.8794330447282</v>
+        <v>40.455842105853</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>1681823306</v>
+        <v>1681823316</v>
       </c>
       <c r="B14" t="n">
         <v>10</v>
       </c>
       <c r="C14" t="n">
-        <v>152.3</v>
+        <v>157.6</v>
       </c>
       <c r="D14" t="n">
-        <v>40.93572596767061</v>
+        <v>40.26629058908589</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>1681823307</v>
+        <v>1681823317</v>
       </c>
       <c r="B15" t="n">
         <v>10</v>
       </c>
       <c r="C15" t="n">
-        <v>155.1</v>
+        <v>155.5</v>
       </c>
       <c r="D15" t="n">
-        <v>40.79148807370999</v>
+        <v>40.31012759650128</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>1681823308</v>
+        <v>1681823318</v>
       </c>
       <c r="B16" t="n">
         <v>10</v>
       </c>
       <c r="C16" t="n">
-        <v>152.2</v>
+        <v>157</v>
       </c>
       <c r="D16" t="n">
-        <v>40.77250345618324</v>
+        <v>40.42631185094857</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>1681823309</v>
+        <v>1681823319</v>
       </c>
       <c r="B17" t="n">
         <v>10</v>
       </c>
       <c r="C17" t="n">
-        <v>150.5</v>
+        <v>158.4</v>
       </c>
       <c r="D17" t="n">
-        <v>40.64237352285405</v>
+        <v>40.36523189403086</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>1681823310</v>
+        <v>1681823320</v>
       </c>
       <c r="B18" t="n">
         <v>10</v>
       </c>
       <c r="C18" t="n">
-        <v>146.6</v>
+        <v>158.4</v>
       </c>
       <c r="D18" t="n">
-        <v>40.78167782628478</v>
+        <v>40.32682840257102</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>1681823311</v>
+        <v>1681823321</v>
       </c>
       <c r="B19" t="n">
         <v>10</v>
       </c>
       <c r="C19" t="n">
-        <v>151.1</v>
+        <v>154.2</v>
       </c>
       <c r="D19" t="n">
-        <v>40.63880730350063</v>
+        <v>40.53460666509624</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>1681823312</v>
+        <v>1681823323</v>
       </c>
       <c r="B20" t="n">
         <v>10</v>
       </c>
       <c r="C20" t="n">
-        <v>150.6</v>
+        <v>156.2</v>
       </c>
       <c r="D20" t="n">
-        <v>40.59672463925506</v>
+        <v>40.56075967640994</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>1681823313</v>
+        <v>1681823324</v>
       </c>
       <c r="B21" t="n">
         <v>10</v>
       </c>
       <c r="C21" t="n">
-        <v>152.5</v>
+        <v>153.1</v>
       </c>
       <c r="D21" t="n">
-        <v>40.45908164104623</v>
+        <v>40.4126579864492</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>1681823314</v>
+        <v>1681823325</v>
       </c>
       <c r="B22" t="n">
         <v>10</v>
       </c>
       <c r="C22" t="n">
-        <v>153.3</v>
+        <v>148.8</v>
       </c>
       <c r="D22" t="n">
-        <v>40.5832706935822</v>
+        <v>40.43544269152704</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>1681823315</v>
+        <v>1681823326</v>
       </c>
       <c r="B23" t="n">
         <v>10</v>
       </c>
       <c r="C23" t="n">
-        <v>156.2</v>
+        <v>151.2</v>
       </c>
       <c r="D23" t="n">
-        <v>40.455842105853</v>
+        <v>40.44476691062736</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>1681823316</v>
+        <v>1681823327</v>
       </c>
       <c r="B24" t="n">
         <v>10</v>
       </c>
       <c r="C24" t="n">
-        <v>157.6</v>
+        <v>152.1</v>
       </c>
       <c r="D24" t="n">
-        <v>40.26629058908589</v>
+        <v>40.52362317103173</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>1681823317</v>
+        <v>1681823328</v>
       </c>
       <c r="B25" t="n">
         <v>10</v>
       </c>
       <c r="C25" t="n">
-        <v>155.5</v>
+        <v>153.2</v>
       </c>
       <c r="D25" t="n">
-        <v>40.31012759650128</v>
+        <v>40.69018688619737</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>1681823318</v>
+        <v>1681823329</v>
       </c>
       <c r="B26" t="n">
         <v>10</v>
       </c>
       <c r="C26" t="n">
-        <v>157</v>
+        <v>148.4</v>
       </c>
       <c r="D26" t="n">
-        <v>40.42631185094857</v>
+        <v>40.63901031446685</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>1681823319</v>
+        <v>1681823330</v>
       </c>
       <c r="B27" t="n">
         <v>10</v>
       </c>
       <c r="C27" t="n">
-        <v>158.4</v>
+        <v>147.6</v>
       </c>
       <c r="D27" t="n">
-        <v>40.36523189403086</v>
+        <v>40.70180774444425</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>1681823320</v>
+        <v>1681823331</v>
       </c>
       <c r="B28" t="n">
         <v>10</v>
       </c>
       <c r="C28" t="n">
-        <v>158.4</v>
+        <v>150.5</v>
       </c>
       <c r="D28" t="n">
-        <v>40.32682840257102</v>
+        <v>40.75583891290667</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>1681823321</v>
+        <v>1681823332</v>
       </c>
       <c r="B29" t="n">
         <v>10</v>
       </c>
       <c r="C29" t="n">
-        <v>154.2</v>
+        <v>147.9</v>
       </c>
       <c r="D29" t="n">
-        <v>40.53460666509624</v>
+        <v>40.74927138686342</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>1681823323</v>
+        <v>1681823333</v>
       </c>
       <c r="B30" t="n">
         <v>10</v>
       </c>
       <c r="C30" t="n">
-        <v>156.2</v>
+        <v>148.1</v>
       </c>
       <c r="D30" t="n">
-        <v>40.56075967640994</v>
+        <v>40.61119837421456</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>1681823324</v>
+        <v>1681823334</v>
       </c>
       <c r="B31" t="n">
         <v>10</v>
       </c>
       <c r="C31" t="n">
-        <v>153.1</v>
+        <v>149.2</v>
       </c>
       <c r="D31" t="n">
-        <v>40.4126579864492</v>
+        <v>40.49966628416506</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>1681823325</v>
+        <v>1681823335</v>
       </c>
       <c r="B32" t="n">
         <v>10</v>
       </c>
       <c r="C32" t="n">
-        <v>148.8</v>
+        <v>152.9</v>
       </c>
       <c r="D32" t="n">
-        <v>40.43544269152704</v>
+        <v>40.3910976171252</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>1681823326</v>
+        <v>1681823336</v>
       </c>
       <c r="B33" t="n">
         <v>10</v>
       </c>
       <c r="C33" t="n">
-        <v>151.2</v>
+        <v>151.3</v>
       </c>
       <c r="D33" t="n">
-        <v>40.44476691062736</v>
+        <v>40.37816641420996</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>1681823327</v>
+        <v>1681823337</v>
       </c>
       <c r="B34" t="n">
         <v>10</v>
       </c>
       <c r="C34" t="n">
-        <v>152.1</v>
+        <v>156.2</v>
       </c>
       <c r="D34" t="n">
-        <v>40.52362317103173</v>
+        <v>40.35230614539696</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>1681823328</v>
+        <v>1681823338</v>
       </c>
       <c r="B35" t="n">
         <v>10</v>
       </c>
       <c r="C35" t="n">
-        <v>153.2</v>
+        <v>154.7</v>
       </c>
       <c r="D35" t="n">
-        <v>40.69018688619737</v>
+        <v>40.33461453252352</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>1681823329</v>
+        <v>1681823339</v>
       </c>
       <c r="B36" t="n">
         <v>10</v>
       </c>
       <c r="C36" t="n">
-        <v>148.4</v>
+        <v>158</v>
       </c>
       <c r="D36" t="n">
-        <v>40.63901031446685</v>
+        <v>40.22611489793466</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>1681823330</v>
+        <v>1681823340</v>
       </c>
       <c r="B37" t="n">
         <v>10</v>
       </c>
       <c r="C37" t="n">
-        <v>147.6</v>
+        <v>157.7</v>
       </c>
       <c r="D37" t="n">
-        <v>40.70180774444425</v>
+        <v>40.2729186841029</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>1681823331</v>
+        <v>1681823341</v>
       </c>
       <c r="B38" t="n">
         <v>10</v>
       </c>
       <c r="C38" t="n">
-        <v>150.5</v>
+        <v>157.8</v>
       </c>
       <c r="D38" t="n">
-        <v>40.75583891290667</v>
+        <v>40.27898811005257</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>1681823332</v>
+        <v>1681823342</v>
       </c>
       <c r="B39" t="n">
         <v>10</v>
       </c>
       <c r="C39" t="n">
-        <v>147.9</v>
+        <v>159.7</v>
       </c>
       <c r="D39" t="n">
-        <v>40.74927138686342</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>1681823333</v>
-      </c>
-      <c r="B40" t="n">
-        <v>10</v>
-      </c>
-      <c r="C40" t="n">
-        <v>148.1</v>
-      </c>
-      <c r="D40" t="n">
-        <v>40.61119837421456</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>1681823334</v>
-      </c>
-      <c r="B41" t="n">
-        <v>10</v>
-      </c>
-      <c r="C41" t="n">
-        <v>149.2</v>
-      </c>
-      <c r="D41" t="n">
-        <v>40.49966628416506</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>1681823335</v>
-      </c>
-      <c r="B42" t="n">
-        <v>10</v>
-      </c>
-      <c r="C42" t="n">
-        <v>152.9</v>
-      </c>
-      <c r="D42" t="n">
-        <v>40.3910976171252</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>1681823336</v>
-      </c>
-      <c r="B43" t="n">
-        <v>10</v>
-      </c>
-      <c r="C43" t="n">
-        <v>151.3</v>
-      </c>
-      <c r="D43" t="n">
-        <v>40.37816641420996</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>1681823337</v>
-      </c>
-      <c r="B44" t="n">
-        <v>10</v>
-      </c>
-      <c r="C44" t="n">
-        <v>156.2</v>
-      </c>
-      <c r="D44" t="n">
-        <v>40.35230614539696</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>1681823338</v>
-      </c>
-      <c r="B45" t="n">
-        <v>10</v>
-      </c>
-      <c r="C45" t="n">
-        <v>154.7</v>
-      </c>
-      <c r="D45" t="n">
-        <v>40.33461453252352</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>1681823339</v>
-      </c>
-      <c r="B46" t="n">
-        <v>10</v>
-      </c>
-      <c r="C46" t="n">
-        <v>158</v>
-      </c>
-      <c r="D46" t="n">
-        <v>40.22611489793466</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>1681823340</v>
-      </c>
-      <c r="B47" t="n">
-        <v>10</v>
-      </c>
-      <c r="C47" t="n">
-        <v>157.7</v>
-      </c>
-      <c r="D47" t="n">
-        <v>40.2729186841029</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>1681823341</v>
-      </c>
-      <c r="B48" t="n">
-        <v>10</v>
-      </c>
-      <c r="C48" t="n">
-        <v>157.8</v>
-      </c>
-      <c r="D48" t="n">
-        <v>40.27898811005257</v>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="n">
-        <v>1681823342</v>
-      </c>
-      <c r="B49" t="n">
-        <v>10</v>
-      </c>
-      <c r="C49" t="n">
-        <v>159.7</v>
-      </c>
-      <c r="D49" t="n">
         <v>40.32247315378899</v>
       </c>
     </row>
